--- a/project/table_tools/table/EffectData.xlsx
+++ b/project/table_tools/table/EffectData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\QiYou_Projects\WestJourney\table\client\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyGitHub\DrawAvatar\table\client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD9E616-5024-4C47-ADE5-C43D54EAC941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DB05CD-3083-4BCC-BC74-9097C5BFF1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EffectData" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="131">
   <si>
     <t>名称</t>
   </si>
@@ -681,23 +681,6 @@
   </si>
   <si>
     <t>九界冲刺蓝</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00000000</t>
-    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -906,7 +889,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1019,9 +1002,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1420,12 +1400,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
     <col min="2" max="2" width="34.25" customWidth="1"/>
-    <col min="3" max="3" width="42.125" style="39" customWidth="1"/>
+    <col min="3" max="3" width="42.125" style="38" customWidth="1"/>
     <col min="4" max="4" width="15.75" style="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1463,7 +1443,7 @@
         <v>44</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5">
@@ -1579,17 +1559,17 @@
     </row>
     <row r="13" spans="1:5" s="10" customFormat="1" ht="16.5">
       <c r="A13" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>36</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="26" customFormat="1" ht="16.5">
@@ -1854,243 +1834,243 @@
       </c>
       <c r="E33" s="25"/>
     </row>
-    <row r="34" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A34" s="40">
+    <row r="34" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A34" s="39">
         <v>20000</v>
       </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="42" t="s">
+      <c r="B34" s="40"/>
+      <c r="C34" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E34" s="41" t="s">
+      <c r="D34" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="40" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A35" s="40" t="s">
+    <row r="35" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A35" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="41"/>
-      <c r="C35" s="44" t="s">
+      <c r="B35" s="40"/>
+      <c r="C35" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D35" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="41"/>
-    </row>
-    <row r="36" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A36" s="40" t="s">
+      <c r="D35" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="40"/>
+    </row>
+    <row r="36" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A36" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="B36" s="41"/>
-      <c r="C36" s="44" t="s">
+      <c r="B36" s="40"/>
+      <c r="C36" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D36" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E36" s="41"/>
-    </row>
-    <row r="37" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A37" s="40" t="s">
+      <c r="D36" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="40"/>
+    </row>
+    <row r="37" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A37" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B37" s="41"/>
-      <c r="C37" s="44" t="s">
+      <c r="B37" s="40"/>
+      <c r="C37" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E37" s="41"/>
-    </row>
-    <row r="38" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A38" s="40" t="s">
+      <c r="D37" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="40"/>
+    </row>
+    <row r="38" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A38" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="B38" s="41"/>
-      <c r="C38" s="45" t="s">
+      <c r="B38" s="40"/>
+      <c r="C38" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" s="41"/>
-    </row>
-    <row r="39" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A39" s="40" t="s">
+      <c r="D38" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="40"/>
+    </row>
+    <row r="39" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A39" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="41"/>
-      <c r="C39" s="44" t="s">
+      <c r="B39" s="40"/>
+      <c r="C39" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="D39" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" s="41"/>
-    </row>
-    <row r="40" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A40" s="40" t="s">
+      <c r="D39" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" s="40"/>
+    </row>
+    <row r="40" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A40" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="41"/>
-      <c r="C40" s="45" t="s">
+      <c r="B40" s="40"/>
+      <c r="C40" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="D40" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E40" s="41"/>
-    </row>
-    <row r="41" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A41" s="40" t="s">
+      <c r="D40" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" s="40"/>
+    </row>
+    <row r="41" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A41" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="41"/>
-      <c r="C41" s="44" t="s">
+      <c r="B41" s="40"/>
+      <c r="C41" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="D41" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" s="41"/>
-    </row>
-    <row r="42" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A42" s="40" t="s">
+      <c r="D41" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="40"/>
+    </row>
+    <row r="42" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A42" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B42" s="41"/>
-      <c r="C42" s="45" t="s">
+      <c r="B42" s="40"/>
+      <c r="C42" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E42" s="41"/>
-    </row>
-    <row r="43" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A43" s="40" t="s">
+      <c r="D42" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="40"/>
+    </row>
+    <row r="43" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A43" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="41"/>
-      <c r="C43" s="44" t="s">
+      <c r="B43" s="40"/>
+      <c r="C43" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="D43" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E43" s="41"/>
-    </row>
-    <row r="44" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A44" s="40" t="s">
+      <c r="D43" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" s="40"/>
+    </row>
+    <row r="44" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A44" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="41"/>
-      <c r="C44" s="45" t="s">
+      <c r="B44" s="40"/>
+      <c r="C44" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E44" s="41"/>
-    </row>
-    <row r="45" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A45" s="40" t="s">
+      <c r="D44" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="40"/>
+    </row>
+    <row r="45" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A45" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B45" s="41"/>
-      <c r="C45" s="44" t="s">
+      <c r="B45" s="40"/>
+      <c r="C45" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E45" s="41"/>
-    </row>
-    <row r="46" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A46" s="40" t="s">
+      <c r="D45" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="40"/>
+    </row>
+    <row r="46" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A46" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B46" s="41"/>
-      <c r="C46" s="45" t="s">
+      <c r="B46" s="40"/>
+      <c r="C46" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E46" s="41"/>
-    </row>
-    <row r="47" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A47" s="40" t="s">
+      <c r="D46" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" s="40"/>
+    </row>
+    <row r="47" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A47" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B47" s="41"/>
-      <c r="C47" s="44" t="s">
+      <c r="B47" s="40"/>
+      <c r="C47" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="D47" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E47" s="41"/>
-    </row>
-    <row r="48" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A48" s="40" t="s">
+      <c r="D47" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" s="40"/>
+    </row>
+    <row r="48" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A48" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="B48" s="41"/>
-      <c r="C48" s="45" t="s">
+      <c r="B48" s="40"/>
+      <c r="C48" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="D48" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E48" s="41"/>
-    </row>
-    <row r="49" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A49" s="40" t="s">
+      <c r="D48" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" s="40"/>
+    </row>
+    <row r="49" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A49" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="B49" s="41"/>
-      <c r="C49" s="44" t="s">
+      <c r="B49" s="40"/>
+      <c r="C49" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="D49" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E49" s="41"/>
-    </row>
-    <row r="50" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A50" s="40" t="s">
+      <c r="D49" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="40"/>
+    </row>
+    <row r="50" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A50" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="B50" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="C50" s="44" t="s">
+      <c r="D50" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" s="40"/>
+    </row>
+    <row r="51" spans="1:5" s="42" customFormat="1" ht="16.5">
+      <c r="A51" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="D50" s="40" t="s">
+      <c r="B51" s="40"/>
+      <c r="C51" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="E50" s="41"/>
-    </row>
-    <row r="51" spans="1:5" s="43" customFormat="1" ht="16.5">
-      <c r="A51" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B51" s="41"/>
-      <c r="C51" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="D51" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E51" s="41"/>
+      <c r="D51" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="40"/>
     </row>
     <row r="52" spans="1:5" s="29" customFormat="1" ht="16.5">
       <c r="A52" s="5">
@@ -2335,7 +2315,7 @@
       <c r="B70" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C70" s="46" t="s">
+      <c r="C70" s="45" t="s">
         <v>116</v>
       </c>
       <c r="D70" s="19" t="s">
@@ -2349,22 +2329,15 @@
       <c r="A71" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B71" s="48" t="s">
+      <c r="B71" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="C71" s="47" t="s">
+      <c r="C71" s="46" t="s">
         <v>117</v>
       </c>
       <c r="D71" s="20" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" s="8" customFormat="1">
-      <c r="A72" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C72" s="38"/>
-      <c r="D72" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
